--- a/artfynd/A 739-2026 artfynd.xlsx
+++ b/artfynd/A 739-2026 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133784443</v>
+        <v>133784440</v>
       </c>
       <c r="B3" t="n">
-        <v>79117</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133784440</v>
+        <v>133784443</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1108,57 +1108,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133784435</v>
+        <v>133784414</v>
       </c>
       <c r="B6" t="n">
-        <v>58079</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727113</v>
+        <v>727054</v>
       </c>
       <c r="R6" t="n">
-        <v>7169772</v>
+        <v>7169921</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1200,7 +1188,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Foto</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,32 +1220,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133784462</v>
+        <v>133784364</v>
       </c>
       <c r="B7" t="n">
-        <v>93257</v>
+        <v>79978</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1262,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>727261</v>
+        <v>727143</v>
       </c>
       <c r="R7" t="n">
-        <v>7169761</v>
+        <v>7170075</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1307,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,32 +1327,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133784364</v>
+        <v>133784462</v>
       </c>
       <c r="B8" t="n">
-        <v>79978</v>
+        <v>93257</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1369,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>727143</v>
+        <v>727261</v>
       </c>
       <c r="R8" t="n">
-        <v>7170075</v>
+        <v>7169761</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1414,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,45 +1434,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133784414</v>
+        <v>133784435</v>
       </c>
       <c r="B9" t="n">
-        <v>79359</v>
+        <v>58079</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>727054</v>
+        <v>727113</v>
       </c>
       <c r="R9" t="n">
-        <v>7169921</v>
+        <v>7169772</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,7 +1516,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1521,12 +1526,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Foto</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1874,10 +1874,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133784366</v>
+        <v>133784472</v>
       </c>
       <c r="B13" t="n">
-        <v>79025</v>
+        <v>79359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1885,21 +1885,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>727131</v>
+        <v>727294</v>
       </c>
       <c r="R13" t="n">
-        <v>7170073</v>
+        <v>7169964</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2088,10 +2088,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133784472</v>
+        <v>133784366</v>
       </c>
       <c r="B15" t="n">
-        <v>79359</v>
+        <v>79025</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,21 +2099,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>727294</v>
+        <v>727131</v>
       </c>
       <c r="R15" t="n">
-        <v>7169964</v>
+        <v>7170073</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2623,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133784369</v>
+        <v>133784347</v>
       </c>
       <c r="B20" t="n">
-        <v>79359</v>
+        <v>79117</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>727137</v>
+        <v>727279</v>
       </c>
       <c r="R20" t="n">
-        <v>7170057</v>
+        <v>7170102</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133784347</v>
+        <v>133784369</v>
       </c>
       <c r="B22" t="n">
-        <v>79117</v>
+        <v>79359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2848,21 +2848,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>727279</v>
+        <v>727137</v>
       </c>
       <c r="R22" t="n">
-        <v>7170102</v>
+        <v>7170057</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3051,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133784365</v>
+        <v>133784448</v>
       </c>
       <c r="B24" t="n">
-        <v>79978</v>
+        <v>79117</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3062,21 +3062,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>727127</v>
+        <v>727172</v>
       </c>
       <c r="R24" t="n">
-        <v>7170081</v>
+        <v>7169745</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3158,10 +3158,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133784448</v>
+        <v>133784365</v>
       </c>
       <c r="B25" t="n">
-        <v>79117</v>
+        <v>79978</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3169,21 +3169,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>727172</v>
+        <v>727127</v>
       </c>
       <c r="R25" t="n">
-        <v>7169745</v>
+        <v>7170081</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3265,32 +3265,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133784367</v>
+        <v>133784348</v>
       </c>
       <c r="B26" t="n">
-        <v>92206</v>
+        <v>79359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>727144</v>
+        <v>727224</v>
       </c>
       <c r="R26" t="n">
-        <v>7170052</v>
+        <v>7170092</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3345,12 +3345,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Bilder</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3377,32 +3372,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133784371</v>
+        <v>133784367</v>
       </c>
       <c r="B27" t="n">
-        <v>79978</v>
+        <v>92206</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3412,10 +3407,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>727126</v>
+        <v>727144</v>
       </c>
       <c r="R27" t="n">
-        <v>7170061</v>
+        <v>7170052</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3447,7 +3442,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3457,7 +3452,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Bilder</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3484,53 +3484,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133784368</v>
+        <v>133784371</v>
       </c>
       <c r="B28" t="n">
-        <v>58658</v>
+        <v>79978</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103044</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>727132</v>
+        <v>727126</v>
       </c>
       <c r="R28" t="n">
-        <v>7170063</v>
+        <v>7170061</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3562,7 +3554,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3572,7 +3564,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3599,45 +3591,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133784348</v>
+        <v>133784368</v>
       </c>
       <c r="B29" t="n">
-        <v>79359</v>
+        <v>58658</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>103044</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>727224</v>
+        <v>727132</v>
       </c>
       <c r="R29" t="n">
-        <v>7170092</v>
+        <v>7170063</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3813,32 +3813,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133784346</v>
+        <v>133784415</v>
       </c>
       <c r="B31" t="n">
-        <v>79359</v>
+        <v>93257</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>727295</v>
+        <v>727011</v>
       </c>
       <c r="R31" t="n">
-        <v>7170114</v>
+        <v>7169887</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3920,32 +3920,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133784415</v>
+        <v>133784438</v>
       </c>
       <c r="B32" t="n">
-        <v>93257</v>
+        <v>92013</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>727011</v>
+        <v>727106</v>
       </c>
       <c r="R32" t="n">
-        <v>7169887</v>
+        <v>7169739</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4027,10 +4027,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133784438</v>
+        <v>133784346</v>
       </c>
       <c r="B33" t="n">
-        <v>92013</v>
+        <v>79359</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4038,21 +4038,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4062,10 +4062,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>727106</v>
+        <v>727295</v>
       </c>
       <c r="R33" t="n">
-        <v>7169739</v>
+        <v>7170114</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4249,45 +4249,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133784459</v>
+        <v>133784458</v>
       </c>
       <c r="B35" t="n">
-        <v>79117</v>
+        <v>58349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>727225</v>
+        <v>727223</v>
       </c>
       <c r="R35" t="n">
-        <v>7169739</v>
+        <v>7169745</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4319,7 +4327,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4329,7 +4337,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4356,53 +4364,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133784458</v>
+        <v>133784459</v>
       </c>
       <c r="B36" t="n">
-        <v>58349</v>
+        <v>79117</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>727223</v>
+        <v>727225</v>
       </c>
       <c r="R36" t="n">
-        <v>7169745</v>
+        <v>7169739</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4471,45 +4471,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133784446</v>
+        <v>133784406</v>
       </c>
       <c r="B37" t="n">
-        <v>79359</v>
+        <v>58079</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>727148</v>
+        <v>727006</v>
       </c>
       <c r="R37" t="n">
-        <v>7169748</v>
+        <v>7169971</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4541,7 +4549,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4551,12 +4559,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Foto 3</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4583,10 +4586,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133784475</v>
+        <v>133784469</v>
       </c>
       <c r="B38" t="n">
-        <v>79359</v>
+        <v>79116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4594,21 +4597,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4618,10 +4621,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>727290</v>
+        <v>727278</v>
       </c>
       <c r="R38" t="n">
-        <v>7170047</v>
+        <v>7169903</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4653,7 +4656,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4663,7 +4666,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4690,53 +4693,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133784406</v>
+        <v>133784475</v>
       </c>
       <c r="B39" t="n">
-        <v>58079</v>
+        <v>79359</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>727006</v>
+        <v>727290</v>
       </c>
       <c r="R39" t="n">
-        <v>7169971</v>
+        <v>7170047</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4768,7 +4763,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4778,7 +4773,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4912,53 +4907,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133784420</v>
+        <v>133784446</v>
       </c>
       <c r="B41" t="n">
-        <v>58349</v>
+        <v>79359</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>727029</v>
+        <v>727148</v>
       </c>
       <c r="R41" t="n">
-        <v>7169893</v>
+        <v>7169748</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4990,7 +4977,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5000,12 +4987,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Foto 3</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5032,45 +5019,53 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133784469</v>
+        <v>133784420</v>
       </c>
       <c r="B42" t="n">
-        <v>79116</v>
+        <v>58349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>727278</v>
+        <v>727029</v>
       </c>
       <c r="R42" t="n">
-        <v>7169903</v>
+        <v>7169893</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5102,7 +5097,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5112,7 +5107,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5139,7 +5139,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133784452</v>
+        <v>133784470</v>
       </c>
       <c r="B43" t="n">
         <v>79978</v>
@@ -5174,10 +5174,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>727172</v>
+        <v>727278</v>
       </c>
       <c r="R43" t="n">
-        <v>7169745</v>
+        <v>7169903</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5246,10 +5246,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133784417</v>
+        <v>133784452</v>
       </c>
       <c r="B44" t="n">
-        <v>79359</v>
+        <v>79978</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5257,21 +5257,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>726999</v>
+        <v>727172</v>
       </c>
       <c r="R44" t="n">
-        <v>7169889</v>
+        <v>7169745</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5326,12 +5326,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Foto 2</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5358,10 +5353,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133784470</v>
+        <v>133784417</v>
       </c>
       <c r="B45" t="n">
-        <v>79978</v>
+        <v>79359</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5369,21 +5364,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5393,10 +5388,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>727278</v>
+        <v>726999</v>
       </c>
       <c r="R45" t="n">
-        <v>7169903</v>
+        <v>7169889</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5428,7 +5423,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5438,7 +5433,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Foto 2</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5465,32 +5465,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133784473</v>
+        <v>133784457</v>
       </c>
       <c r="B46" t="n">
-        <v>79359</v>
+        <v>80478</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>727270</v>
+        <v>727223</v>
       </c>
       <c r="R46" t="n">
-        <v>7170013</v>
+        <v>7169745</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5572,32 +5572,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133784457</v>
+        <v>133784429</v>
       </c>
       <c r="B47" t="n">
-        <v>80478</v>
+        <v>79117</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>727223</v>
+        <v>727065</v>
       </c>
       <c r="R47" t="n">
-        <v>7169745</v>
+        <v>7169763</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5679,10 +5679,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133784429</v>
+        <v>133784473</v>
       </c>
       <c r="B48" t="n">
-        <v>79117</v>
+        <v>79359</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5690,21 +5690,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5714,10 +5714,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>727065</v>
+        <v>727270</v>
       </c>
       <c r="R48" t="n">
-        <v>7169763</v>
+        <v>7170013</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 739-2026 artfynd.xlsx
+++ b/artfynd/A 739-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133784363</v>
       </c>
       <c r="B2" t="n">
-        <v>79949</v>
+        <v>79956</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133784440</v>
+        <v>133784443</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133784443</v>
+        <v>133784440</v>
       </c>
       <c r="B4" t="n">
-        <v>79117</v>
+        <v>79123</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +999,7 @@
         <v>133784476</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,45 +1108,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133784414</v>
+        <v>133784435</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>58079</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727054</v>
+        <v>727113</v>
       </c>
       <c r="R6" t="n">
-        <v>7169921</v>
+        <v>7169772</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1190,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,12 +1200,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Foto</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,32 +1227,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133784364</v>
+        <v>133784462</v>
       </c>
       <c r="B7" t="n">
-        <v>79978</v>
+        <v>93264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>727143</v>
+        <v>727261</v>
       </c>
       <c r="R7" t="n">
-        <v>7170075</v>
+        <v>7169761</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1297,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1307,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,32 +1334,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133784462</v>
+        <v>133784364</v>
       </c>
       <c r="B8" t="n">
-        <v>93257</v>
+        <v>79985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>727261</v>
+        <v>727143</v>
       </c>
       <c r="R8" t="n">
-        <v>7169761</v>
+        <v>7170075</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1404,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1414,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,57 +1441,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133784435</v>
+        <v>133784414</v>
       </c>
       <c r="B9" t="n">
-        <v>58079</v>
+        <v>79366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>727113</v>
+        <v>727054</v>
       </c>
       <c r="R9" t="n">
-        <v>7169772</v>
+        <v>7169921</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1511,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1526,7 +1521,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Foto</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,7 +1556,7 @@
         <v>133784463</v>
       </c>
       <c r="B10" t="n">
-        <v>80478</v>
+        <v>80485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>133784409</v>
       </c>
       <c r="B12" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133784472</v>
+        <v>133784366</v>
       </c>
       <c r="B13" t="n">
-        <v>79359</v>
+        <v>79032</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1885,21 +1885,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>727294</v>
+        <v>727131</v>
       </c>
       <c r="R13" t="n">
-        <v>7169964</v>
+        <v>7170073</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1984,7 +1984,7 @@
         <v>133784465</v>
       </c>
       <c r="B14" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133784366</v>
+        <v>133784472</v>
       </c>
       <c r="B15" t="n">
-        <v>79025</v>
+        <v>79366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,21 +2099,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>727131</v>
+        <v>727294</v>
       </c>
       <c r="R15" t="n">
-        <v>7170073</v>
+        <v>7169964</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,7 +2198,7 @@
         <v>133784412</v>
       </c>
       <c r="B16" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>133784468</v>
       </c>
       <c r="B17" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>133784424</v>
       </c>
       <c r="B18" t="n">
-        <v>79025</v>
+        <v>79032</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>133784411</v>
       </c>
       <c r="B19" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133784347</v>
+        <v>133784369</v>
       </c>
       <c r="B20" t="n">
-        <v>79117</v>
+        <v>79366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>727279</v>
+        <v>727137</v>
       </c>
       <c r="R20" t="n">
-        <v>7170102</v>
+        <v>7170057</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2733,7 +2733,7 @@
         <v>133784466</v>
       </c>
       <c r="B21" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133784369</v>
+        <v>133784347</v>
       </c>
       <c r="B22" t="n">
-        <v>79359</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2848,21 +2848,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>727137</v>
+        <v>727279</v>
       </c>
       <c r="R22" t="n">
-        <v>7170057</v>
+        <v>7170102</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2947,7 +2947,7 @@
         <v>133784421</v>
       </c>
       <c r="B23" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3051,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133784448</v>
+        <v>133784365</v>
       </c>
       <c r="B24" t="n">
-        <v>79117</v>
+        <v>79985</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3062,21 +3062,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>727172</v>
+        <v>727127</v>
       </c>
       <c r="R24" t="n">
-        <v>7169745</v>
+        <v>7170081</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3158,10 +3158,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133784365</v>
+        <v>133784448</v>
       </c>
       <c r="B25" t="n">
-        <v>79978</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3169,21 +3169,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>727127</v>
+        <v>727172</v>
       </c>
       <c r="R25" t="n">
-        <v>7170081</v>
+        <v>7169745</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3265,32 +3265,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133784348</v>
+        <v>133784367</v>
       </c>
       <c r="B26" t="n">
-        <v>79359</v>
+        <v>92213</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>727224</v>
+        <v>727144</v>
       </c>
       <c r="R26" t="n">
-        <v>7170092</v>
+        <v>7170052</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3345,7 +3345,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Bilder</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3372,32 +3377,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133784367</v>
+        <v>133784371</v>
       </c>
       <c r="B27" t="n">
-        <v>92206</v>
+        <v>79985</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3407,10 +3412,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>727144</v>
+        <v>727126</v>
       </c>
       <c r="R27" t="n">
-        <v>7170052</v>
+        <v>7170061</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3442,7 +3447,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3452,12 +3457,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Bilder</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3484,45 +3484,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133784371</v>
+        <v>133784368</v>
       </c>
       <c r="B28" t="n">
-        <v>79978</v>
+        <v>58658</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>103044</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>727126</v>
+        <v>727132</v>
       </c>
       <c r="R28" t="n">
-        <v>7170061</v>
+        <v>7170063</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3554,7 +3562,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3564,7 +3572,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3591,53 +3599,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133784368</v>
+        <v>133784348</v>
       </c>
       <c r="B29" t="n">
-        <v>58658</v>
+        <v>79366</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>727132</v>
+        <v>727224</v>
       </c>
       <c r="R29" t="n">
-        <v>7170063</v>
+        <v>7170092</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3709,7 +3709,7 @@
         <v>133784478</v>
       </c>
       <c r="B30" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3813,32 +3813,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133784415</v>
+        <v>133784346</v>
       </c>
       <c r="B31" t="n">
-        <v>93257</v>
+        <v>79366</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>727011</v>
+        <v>727295</v>
       </c>
       <c r="R31" t="n">
-        <v>7169887</v>
+        <v>7170114</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3920,32 +3920,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133784438</v>
+        <v>133784415</v>
       </c>
       <c r="B32" t="n">
-        <v>92013</v>
+        <v>93264</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>727106</v>
+        <v>727011</v>
       </c>
       <c r="R32" t="n">
-        <v>7169739</v>
+        <v>7169887</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4027,10 +4027,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133784346</v>
+        <v>133784438</v>
       </c>
       <c r="B33" t="n">
-        <v>79359</v>
+        <v>92020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4038,21 +4038,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4062,10 +4062,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>727295</v>
+        <v>727106</v>
       </c>
       <c r="R33" t="n">
-        <v>7170114</v>
+        <v>7169739</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4249,53 +4249,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133784458</v>
+        <v>133784459</v>
       </c>
       <c r="B35" t="n">
-        <v>58349</v>
+        <v>79124</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>727223</v>
+        <v>727225</v>
       </c>
       <c r="R35" t="n">
-        <v>7169745</v>
+        <v>7169739</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4327,7 +4319,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4337,7 +4329,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4364,45 +4356,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133784459</v>
+        <v>133784458</v>
       </c>
       <c r="B36" t="n">
-        <v>79117</v>
+        <v>58349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>727225</v>
+        <v>727223</v>
       </c>
       <c r="R36" t="n">
-        <v>7169739</v>
+        <v>7169745</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4471,53 +4471,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133784406</v>
+        <v>133784446</v>
       </c>
       <c r="B37" t="n">
-        <v>58079</v>
+        <v>79366</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>727006</v>
+        <v>727148</v>
       </c>
       <c r="R37" t="n">
-        <v>7169971</v>
+        <v>7169748</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4549,7 +4541,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4559,7 +4551,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Foto 3</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4586,10 +4583,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133784469</v>
+        <v>133784475</v>
       </c>
       <c r="B38" t="n">
-        <v>79116</v>
+        <v>79366</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4597,21 +4594,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4621,10 +4618,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>727278</v>
+        <v>727290</v>
       </c>
       <c r="R38" t="n">
-        <v>7169903</v>
+        <v>7170047</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4656,7 +4653,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4666,7 +4663,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4693,45 +4690,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133784475</v>
+        <v>133784406</v>
       </c>
       <c r="B39" t="n">
-        <v>79359</v>
+        <v>58079</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>727290</v>
+        <v>727006</v>
       </c>
       <c r="R39" t="n">
-        <v>7170047</v>
+        <v>7169971</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4763,7 +4768,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4773,7 +4778,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4803,7 +4808,7 @@
         <v>133784350</v>
       </c>
       <c r="B40" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4907,45 +4912,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133784446</v>
+        <v>133784420</v>
       </c>
       <c r="B41" t="n">
-        <v>79359</v>
+        <v>58349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>727148</v>
+        <v>727029</v>
       </c>
       <c r="R41" t="n">
-        <v>7169748</v>
+        <v>7169893</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4977,7 +4990,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4987,12 +5000,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Foto 3</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5019,53 +5032,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133784420</v>
+        <v>133784469</v>
       </c>
       <c r="B42" t="n">
-        <v>58349</v>
+        <v>79123</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103015</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>727029</v>
+        <v>727278</v>
       </c>
       <c r="R42" t="n">
-        <v>7169893</v>
+        <v>7169903</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5097,7 +5102,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5107,12 +5112,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5139,10 +5139,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133784470</v>
+        <v>133784452</v>
       </c>
       <c r="B43" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5174,10 +5174,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>727278</v>
+        <v>727172</v>
       </c>
       <c r="R43" t="n">
-        <v>7169903</v>
+        <v>7169745</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5246,10 +5246,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133784452</v>
+        <v>133784417</v>
       </c>
       <c r="B44" t="n">
-        <v>79978</v>
+        <v>79366</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5257,21 +5257,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>727172</v>
+        <v>726999</v>
       </c>
       <c r="R44" t="n">
-        <v>7169745</v>
+        <v>7169889</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5326,7 +5326,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Foto 2</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5353,10 +5358,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133784417</v>
+        <v>133784470</v>
       </c>
       <c r="B45" t="n">
-        <v>79359</v>
+        <v>79985</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5364,21 +5369,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5388,10 +5393,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>726999</v>
+        <v>727278</v>
       </c>
       <c r="R45" t="n">
-        <v>7169889</v>
+        <v>7169903</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5423,7 +5428,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5433,12 +5438,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Foto 2</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5465,32 +5465,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133784457</v>
+        <v>133784473</v>
       </c>
       <c r="B46" t="n">
-        <v>80478</v>
+        <v>79366</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>727223</v>
+        <v>727270</v>
       </c>
       <c r="R46" t="n">
-        <v>7169745</v>
+        <v>7170013</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5572,32 +5572,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133784429</v>
+        <v>133784457</v>
       </c>
       <c r="B47" t="n">
-        <v>79117</v>
+        <v>80485</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>727065</v>
+        <v>727223</v>
       </c>
       <c r="R47" t="n">
-        <v>7169763</v>
+        <v>7169745</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5679,10 +5679,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133784473</v>
+        <v>133784429</v>
       </c>
       <c r="B48" t="n">
-        <v>79359</v>
+        <v>79124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5690,21 +5690,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5714,10 +5714,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>727270</v>
+        <v>727065</v>
       </c>
       <c r="R48" t="n">
-        <v>7170013</v>
+        <v>7169763</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 739-2026 artfynd.xlsx
+++ b/artfynd/A 739-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133784363</v>
+        <v>133784367</v>
       </c>
       <c r="B2" t="n">
-        <v>79956</v>
+        <v>92220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727161</v>
+        <v>727144</v>
       </c>
       <c r="R2" t="n">
-        <v>7170095</v>
+        <v>7170052</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bilder</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133784443</v>
+        <v>133784360</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727166</v>
+        <v>727168</v>
       </c>
       <c r="R3" t="n">
-        <v>7169724</v>
+        <v>7170101</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133784440</v>
+        <v>133784366</v>
       </c>
       <c r="B4" t="n">
-        <v>79123</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727166</v>
+        <v>727131</v>
       </c>
       <c r="R4" t="n">
-        <v>7169724</v>
+        <v>7170073</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133784476</v>
+        <v>133784424</v>
       </c>
       <c r="B5" t="n">
-        <v>79366</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727291</v>
+        <v>727038</v>
       </c>
       <c r="R5" t="n">
-        <v>7170069</v>
+        <v>7169837</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,12 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera bålar på flera träd</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,57 +1108,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133784435</v>
+        <v>133784359</v>
       </c>
       <c r="B6" t="n">
-        <v>58079</v>
+        <v>92027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727113</v>
+        <v>727164</v>
       </c>
       <c r="R6" t="n">
-        <v>7169772</v>
+        <v>7170110</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1200,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,32 +1215,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133784462</v>
+        <v>133784427</v>
       </c>
       <c r="B7" t="n">
-        <v>93264</v>
+        <v>92027</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1262,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>727261</v>
+        <v>727055</v>
       </c>
       <c r="R7" t="n">
-        <v>7169761</v>
+        <v>7169750</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1307,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133784364</v>
+        <v>133784438</v>
       </c>
       <c r="B8" t="n">
-        <v>79985</v>
+        <v>92027</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1345,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1369,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>727143</v>
+        <v>727106</v>
       </c>
       <c r="R8" t="n">
-        <v>7170075</v>
+        <v>7169739</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1414,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,32 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133784414</v>
+        <v>133784399</v>
       </c>
       <c r="B9" t="n">
-        <v>79366</v>
+        <v>96410</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2812</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1476,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>727054</v>
+        <v>726989</v>
       </c>
       <c r="R9" t="n">
-        <v>7169921</v>
+        <v>7170041</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1521,12 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Foto</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,32 +1536,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133784463</v>
+        <v>133784415</v>
       </c>
       <c r="B10" t="n">
-        <v>80485</v>
+        <v>93271</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>727258</v>
+        <v>727011</v>
       </c>
       <c r="R10" t="n">
-        <v>7169782</v>
+        <v>7169887</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1633,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,32 +1643,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133784453</v>
+        <v>133784462</v>
       </c>
       <c r="B11" t="n">
-        <v>58349</v>
+        <v>93271</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>727193</v>
+        <v>727261</v>
       </c>
       <c r="R11" t="n">
-        <v>7169744</v>
+        <v>7169761</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,7 +1713,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1723,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,14 +1750,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133784409</v>
+        <v>133784346</v>
       </c>
       <c r="B12" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1802,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>727028</v>
+        <v>727295</v>
       </c>
       <c r="R12" t="n">
-        <v>7169978</v>
+        <v>7170114</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1847,7 +1830,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133784366</v>
+        <v>133784348</v>
       </c>
       <c r="B13" t="n">
-        <v>79032</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1909,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>727131</v>
+        <v>727224</v>
       </c>
       <c r="R13" t="n">
-        <v>7170073</v>
+        <v>7170092</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,7 +1927,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1954,7 +1937,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1981,14 +1964,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133784465</v>
+        <v>133784354</v>
       </c>
       <c r="B14" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2016,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>727291</v>
+        <v>727185</v>
       </c>
       <c r="R14" t="n">
-        <v>7169816</v>
+        <v>7170118</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,7 +2034,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2061,7 +2044,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,14 +2071,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133784472</v>
+        <v>133784369</v>
       </c>
       <c r="B15" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2123,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>727294</v>
+        <v>727137</v>
       </c>
       <c r="R15" t="n">
-        <v>7169964</v>
+        <v>7170057</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2168,7 +2151,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2195,14 +2178,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133784412</v>
+        <v>133784409</v>
       </c>
       <c r="B16" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2230,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>727060</v>
+        <v>727028</v>
       </c>
       <c r="R16" t="n">
-        <v>7169923</v>
+        <v>7169978</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2275,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,14 +2285,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133784468</v>
+        <v>133784411</v>
       </c>
       <c r="B17" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2337,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>727289</v>
+        <v>727026</v>
       </c>
       <c r="R17" t="n">
-        <v>7169901</v>
+        <v>7169973</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2382,7 +2365,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,32 +2392,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133784424</v>
+        <v>133784412</v>
       </c>
       <c r="B18" t="n">
-        <v>79032</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2444,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>727038</v>
+        <v>727060</v>
       </c>
       <c r="R18" t="n">
-        <v>7169837</v>
+        <v>7169923</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,7 +2462,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2489,7 +2472,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2516,14 +2499,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133784411</v>
+        <v>133784414</v>
       </c>
       <c r="B19" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2551,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>727026</v>
+        <v>727054</v>
       </c>
       <c r="R19" t="n">
-        <v>7169973</v>
+        <v>7169921</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2586,7 +2569,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2596,7 +2579,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Foto</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2623,14 +2611,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133784369</v>
+        <v>133784417</v>
       </c>
       <c r="B20" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2658,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>727137</v>
+        <v>726999</v>
       </c>
       <c r="R20" t="n">
-        <v>7170057</v>
+        <v>7169889</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,7 +2681,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2703,7 +2691,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Foto 2</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2730,32 +2723,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133784466</v>
+        <v>133784421</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2758,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>727294</v>
+        <v>727023</v>
       </c>
       <c r="R21" t="n">
-        <v>7169820</v>
+        <v>7169849</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,7 +2793,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2810,7 +2803,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2837,32 +2830,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133784347</v>
+        <v>133784446</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2872,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>727279</v>
+        <v>727148</v>
       </c>
       <c r="R22" t="n">
-        <v>7170102</v>
+        <v>7169748</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2900,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2917,7 +2910,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Foto 3</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2944,14 +2942,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133784421</v>
+        <v>133784465</v>
       </c>
       <c r="B23" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2979,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>727023</v>
+        <v>727291</v>
       </c>
       <c r="R23" t="n">
-        <v>7169849</v>
+        <v>7169816</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,7 +3012,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3024,7 +3022,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3051,32 +3049,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133784365</v>
+        <v>133784468</v>
       </c>
       <c r="B24" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3086,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>727127</v>
+        <v>727289</v>
       </c>
       <c r="R24" t="n">
-        <v>7170081</v>
+        <v>7169901</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,7 +3119,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3131,7 +3129,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3158,32 +3156,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133784448</v>
+        <v>133784472</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3193,10 +3191,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>727172</v>
+        <v>727294</v>
       </c>
       <c r="R25" t="n">
-        <v>7169745</v>
+        <v>7169964</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,7 +3226,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3238,7 +3236,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3265,10 +3263,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133784367</v>
+        <v>133784473</v>
       </c>
       <c r="B26" t="n">
-        <v>92213</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3276,21 +3274,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3300,10 +3298,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>727144</v>
+        <v>727270</v>
       </c>
       <c r="R26" t="n">
-        <v>7170052</v>
+        <v>7170013</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3335,7 +3333,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3345,12 +3343,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Bilder</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3377,32 +3370,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133784371</v>
+        <v>133784475</v>
       </c>
       <c r="B27" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3412,10 +3405,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>727126</v>
+        <v>727290</v>
       </c>
       <c r="R27" t="n">
-        <v>7170061</v>
+        <v>7170047</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3447,7 +3440,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3457,7 +3450,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3484,53 +3477,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133784368</v>
+        <v>133784476</v>
       </c>
       <c r="B28" t="n">
-        <v>58658</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>727132</v>
+        <v>727291</v>
       </c>
       <c r="R28" t="n">
-        <v>7170063</v>
+        <v>7170069</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3562,7 +3547,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3572,7 +3557,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Flera bålar på flera träd</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3599,14 +3589,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133784348</v>
+        <v>133784478</v>
       </c>
       <c r="B29" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3634,10 +3624,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>727224</v>
+        <v>727297</v>
       </c>
       <c r="R29" t="n">
-        <v>7170092</v>
+        <v>7170084</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3669,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3679,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3706,10 +3696,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133784478</v>
+        <v>133784440</v>
       </c>
       <c r="B30" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3717,21 +3707,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3741,10 +3731,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>727297</v>
+        <v>727166</v>
       </c>
       <c r="R30" t="n">
-        <v>7170084</v>
+        <v>7169724</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3776,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3786,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3813,10 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133784346</v>
+        <v>133784469</v>
       </c>
       <c r="B31" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3824,21 +3814,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3848,10 +3838,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>727295</v>
+        <v>727278</v>
       </c>
       <c r="R31" t="n">
-        <v>7170114</v>
+        <v>7169903</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3883,7 +3873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3893,7 +3883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3920,32 +3910,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133784415</v>
+        <v>133784353</v>
       </c>
       <c r="B32" t="n">
-        <v>93264</v>
+        <v>79992</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3955,10 +3945,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>727011</v>
+        <v>727182</v>
       </c>
       <c r="R32" t="n">
-        <v>7169887</v>
+        <v>7170111</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3990,7 +3980,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4000,7 +3990,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4027,10 +4017,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133784438</v>
+        <v>133784364</v>
       </c>
       <c r="B33" t="n">
-        <v>92020</v>
+        <v>79992</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4038,21 +4028,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4062,10 +4052,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>727106</v>
+        <v>727143</v>
       </c>
       <c r="R33" t="n">
-        <v>7169739</v>
+        <v>7170075</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4097,7 +4087,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4107,7 +4097,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4134,53 +4124,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133784418</v>
+        <v>133784365</v>
       </c>
       <c r="B34" t="n">
-        <v>58079</v>
+        <v>79992</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>727033</v>
+        <v>727127</v>
       </c>
       <c r="R34" t="n">
-        <v>7169893</v>
+        <v>7170081</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4212,7 +4194,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4222,7 +4204,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4249,10 +4231,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133784459</v>
+        <v>133784371</v>
       </c>
       <c r="B35" t="n">
-        <v>79124</v>
+        <v>79992</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4260,21 +4242,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4284,10 +4266,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>727225</v>
+        <v>727126</v>
       </c>
       <c r="R35" t="n">
-        <v>7169739</v>
+        <v>7170061</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4319,7 +4301,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4329,7 +4311,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4356,53 +4338,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133784458</v>
+        <v>133784372</v>
       </c>
       <c r="B36" t="n">
-        <v>58349</v>
+        <v>79992</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>727223</v>
+        <v>727124</v>
       </c>
       <c r="R36" t="n">
-        <v>7169745</v>
+        <v>7170093</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4434,7 +4408,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4444,7 +4418,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4471,10 +4445,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133784446</v>
+        <v>133784452</v>
       </c>
       <c r="B37" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4482,21 +4456,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4506,10 +4480,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>727148</v>
+        <v>727172</v>
       </c>
       <c r="R37" t="n">
-        <v>7169748</v>
+        <v>7169745</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4541,7 +4515,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4551,12 +4525,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Foto 3</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4583,10 +4552,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133784475</v>
+        <v>133784470</v>
       </c>
       <c r="B38" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4594,21 +4563,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4618,10 +4587,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>727290</v>
+        <v>727278</v>
       </c>
       <c r="R38" t="n">
-        <v>7170047</v>
+        <v>7169903</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4653,7 +4622,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4663,7 +4632,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4690,10 +4659,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133784406</v>
+        <v>133784457</v>
       </c>
       <c r="B39" t="n">
-        <v>58079</v>
+        <v>80492</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4701,42 +4670,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103031</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>727006</v>
+        <v>727223</v>
       </c>
       <c r="R39" t="n">
-        <v>7169971</v>
+        <v>7169745</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4768,7 +4729,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4778,7 +4739,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4805,32 +4766,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133784350</v>
+        <v>133784463</v>
       </c>
       <c r="B40" t="n">
-        <v>79124</v>
+        <v>80492</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4840,10 +4801,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>727222</v>
+        <v>727258</v>
       </c>
       <c r="R40" t="n">
-        <v>7170091</v>
+        <v>7169782</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4875,7 +4836,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4885,7 +4846,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4912,27 +4873,27 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133784420</v>
+        <v>133784400</v>
       </c>
       <c r="B41" t="n">
-        <v>58349</v>
+        <v>57975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4945,7 +4906,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4955,10 +4916,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>727029</v>
+        <v>727010</v>
       </c>
       <c r="R41" t="n">
-        <v>7169893</v>
+        <v>7170055</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4990,7 +4951,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5000,19 +4961,19 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Uppfläkta barkfläckar på basen av gamla granar. Svårt att artbestämma säkert, samt bedöma ålder</t>
         </is>
       </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG41" t="b">
         <v>0</v>
@@ -5032,45 +4993,53 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133784469</v>
+        <v>133784420</v>
       </c>
       <c r="B42" t="n">
-        <v>79123</v>
+        <v>58349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>727278</v>
+        <v>727029</v>
       </c>
       <c r="R42" t="n">
-        <v>7169903</v>
+        <v>7169893</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5102,7 +5071,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5112,7 +5081,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5139,32 +5113,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133784452</v>
+        <v>133784453</v>
       </c>
       <c r="B43" t="n">
-        <v>79985</v>
+        <v>58349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5174,10 +5148,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>727172</v>
+        <v>727193</v>
       </c>
       <c r="R43" t="n">
-        <v>7169745</v>
+        <v>7169744</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5209,7 +5183,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5219,7 +5193,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5246,45 +5220,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133784417</v>
+        <v>133784458</v>
       </c>
       <c r="B44" t="n">
-        <v>79366</v>
+        <v>58349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>726999</v>
+        <v>727223</v>
       </c>
       <c r="R44" t="n">
-        <v>7169889</v>
+        <v>7169745</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5316,7 +5298,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5326,12 +5308,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Foto 2</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5358,45 +5335,57 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133784470</v>
+        <v>133784370</v>
       </c>
       <c r="B45" t="n">
-        <v>79985</v>
+        <v>58131</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>103023</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>727278</v>
+        <v>727139</v>
       </c>
       <c r="R45" t="n">
-        <v>7169903</v>
+        <v>7170053</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5428,7 +5417,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5438,7 +5427,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ett par, med bomaterial i näbben. Lämplig biotop</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5465,10 +5459,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133784473</v>
+        <v>133784406</v>
       </c>
       <c r="B46" t="n">
-        <v>79366</v>
+        <v>58079</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5476,34 +5470,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>727270</v>
+        <v>727006</v>
       </c>
       <c r="R46" t="n">
-        <v>7170013</v>
+        <v>7169971</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5535,7 +5537,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5545,7 +5547,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5572,45 +5574,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133784457</v>
+        <v>133784418</v>
       </c>
       <c r="B47" t="n">
-        <v>80485</v>
+        <v>58079</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6461</v>
+        <v>103031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>727223</v>
+        <v>727033</v>
       </c>
       <c r="R47" t="n">
-        <v>7169745</v>
+        <v>7169893</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5642,7 +5652,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5652,7 +5662,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5679,10 +5689,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133784429</v>
+        <v>133784435</v>
       </c>
       <c r="B48" t="n">
-        <v>79124</v>
+        <v>58079</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5690,34 +5700,46 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Storningsliden, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>727065</v>
+        <v>727113</v>
       </c>
       <c r="R48" t="n">
-        <v>7169763</v>
+        <v>7169772</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5749,7 +5771,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5759,7 +5781,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5783,6 +5805,1673 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>133784351</v>
+      </c>
+      <c r="B49" t="n">
+        <v>58624</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>727199</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7170109</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>133784368</v>
+      </c>
+      <c r="B50" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>727132</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7170063</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>133784467</v>
+      </c>
+      <c r="B51" t="n">
+        <v>56706</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>727309</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7169833</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>133784477</v>
+      </c>
+      <c r="B52" t="n">
+        <v>56706</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>727311</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7170074</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>133784345</v>
+      </c>
+      <c r="B53" t="n">
+        <v>56925</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>727325</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7170107</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Bild. Låg och värmde sig i solen på block</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>133784347</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>727279</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7170102</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>133784350</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>727222</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7170091</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>133784429</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>727065</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7169763</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>133784443</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>727166</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7169724</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>133784448</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>727172</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7169745</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>133784459</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>727225</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7169739</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>133784466</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>727294</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7169820</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>133784363</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>727161</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7170095</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>133784425</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>727046</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7169765</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>133784357</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Storningsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>727185</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7170118</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 739-2026 artfynd.xlsx
+++ b/artfynd/A 739-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AZ63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784367</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784360</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784366</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784424</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784359</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784427</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784438</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1533,6 +1573,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784399</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784415</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784462</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1854,6 +1909,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784346</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1961,6 +2021,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784348</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2068,6 +2133,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784354</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2175,6 +2245,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784369</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2282,6 +2357,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784409</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2389,6 +2469,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784411</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2496,6 +2581,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784412</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2608,6 +2698,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784414</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2720,6 +2815,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784417</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2827,6 +2927,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784421</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2939,6 +3044,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784446</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3046,6 +3156,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784465</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3153,6 +3268,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784468</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3260,6 +3380,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784472</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3367,6 +3492,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784473</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3474,6 +3604,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784475</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3586,6 +3721,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784476</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3693,6 +3833,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784478</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3800,6 +3945,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784440</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3907,6 +4057,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784469</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4014,6 +4169,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784353</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4121,6 +4281,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784364</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4228,6 +4393,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784365</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4335,6 +4505,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784371</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4442,6 +4617,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784372</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4549,6 +4729,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784452</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4656,6 +4841,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784470</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4763,6 +4953,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784457</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4870,6 +5065,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784463</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4990,6 +5190,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784400</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5110,6 +5315,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784420</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5217,6 +5427,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784453</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5332,6 +5547,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784458</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5456,6 +5676,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784370</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5571,6 +5796,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784406</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5686,6 +5916,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784418</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5805,6 +6040,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784435</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5925,6 +6165,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784351</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6040,6 +6285,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784368</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6160,6 +6410,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784467</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6280,6 +6535,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784477</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6402,6 +6662,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784345</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6509,6 +6774,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784347</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6616,6 +6886,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784350</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6723,6 +6998,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784429</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6830,6 +7110,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784443</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6937,6 +7222,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784448</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7044,6 +7334,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784459</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7151,6 +7446,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784466</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7258,6 +7558,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784363</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7365,6 +7670,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784425</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7472,8 +7782,77 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133784357</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>